--- a/Data/FlightPlan/FPL_28AUG26.xlsx
+++ b/Data/FlightPlan/FPL_28AUG26.xlsx
@@ -506,6 +506,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:22</t>
+  </si>
+  <si>
     <t>09:00</t>
   </si>
   <si>
@@ -752,6 +755,9 @@
     <t>07:45</t>
   </si>
   <si>
+    <t>08:15</t>
+  </si>
+  <si>
     <t>12:40</t>
   </si>
   <si>
@@ -938,6 +944,12 @@
     <t>VN-A643</t>
   </si>
   <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -953,9 +965,6 @@
     <t>VN-A647</t>
   </si>
   <si>
-    <t>08:15</t>
-  </si>
-  <si>
     <t>TBB</t>
   </si>
   <si>
@@ -977,9 +986,6 @@
     <t>10:20</t>
   </si>
   <si>
-    <t>14:20</t>
-  </si>
-  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -1019,9 +1025,6 @@
     <t>08:25</t>
   </si>
   <si>
-    <t>12:35</t>
-  </si>
-  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -1079,18 +1082,18 @@
     <t>05:45</t>
   </si>
   <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
     <t>16:35</t>
   </si>
   <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
     <t>21:55</t>
   </si>
   <si>
@@ -1262,7 +1265,7 @@
     <t>Total Record(s): 426</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 28, 2026 01:00</t>
+    <t xml:space="preserve">Generated on  Aug 28, 2026 02:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4179,7 +4182,9 @@
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c t="s" r="M86" s="7">
+        <v>165</v>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
@@ -4205,10 +4210,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4235,10 +4240,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>107</v>
@@ -4265,13 +4270,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>135</v>
@@ -4307,7 +4312,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4316,13 +4321,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4340,13 +4345,13 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>16</v>
@@ -4373,7 +4378,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4382,10 +4387,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>20</v>
@@ -4406,19 +4411,19 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>39</v>
@@ -4439,7 +4444,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4451,7 +4456,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>149</v>
@@ -4472,7 +4477,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4484,7 +4489,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>107</v>
@@ -4520,7 +4525,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4532,7 +4537,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>87</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4586,7 +4591,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4598,10 +4603,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4619,22 +4624,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
+        <v>179</v>
+      </c>
+      <c r="F101" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G101" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H101" s="8">
+        <v>183</v>
+      </c>
+      <c t="s" r="I101" s="7">
         <v>178</v>
       </c>
-      <c r="F101" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G101" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H101" s="8">
-        <v>182</v>
-      </c>
-      <c t="s" r="I101" s="7">
-        <v>177</v>
-      </c>
       <c t="s" r="J101" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4652,22 +4657,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4700,7 +4705,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4733,7 +4738,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4748,7 +4753,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4766,7 +4771,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4814,7 +4819,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4823,13 +4828,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4847,19 +4852,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>18</v>
@@ -4880,7 +4885,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4889,10 +4894,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>95</v>
@@ -4913,13 +4918,13 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>22</v>
@@ -4946,7 +4951,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4958,7 +4963,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>135</v>
@@ -4994,7 +4999,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5006,10 +5011,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5027,7 +5032,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5042,7 +5047,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5060,7 +5065,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5072,7 +5077,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>36</v>
@@ -5093,7 +5098,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5102,7 +5107,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>138</v>
@@ -5126,13 +5131,13 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
@@ -5159,7 +5164,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5174,7 +5179,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5207,7 +5212,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5219,10 +5224,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5240,7 +5245,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5249,13 +5254,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I122" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5273,13 +5278,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>16</v>
@@ -5306,7 +5311,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5315,7 +5320,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>122</v>
@@ -5339,19 +5344,19 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>117</v>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5387,7 +5392,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5420,7 +5425,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5432,7 +5437,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>137</v>
@@ -5449,11 +5454,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C129" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5482,11 +5487,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C130" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5495,13 +5500,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5515,26 +5520,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5567,7 +5572,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5579,7 +5584,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>34</v>
@@ -5600,7 +5605,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5612,10 +5617,10 @@
         <v>127</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5633,7 +5638,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5645,7 +5650,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>55</v>
@@ -5666,7 +5671,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5678,7 +5683,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>143</v>
@@ -5714,7 +5719,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5726,7 +5731,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>71</v>
@@ -5747,7 +5752,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5795,7 +5800,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5804,13 +5809,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5828,13 +5833,13 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>32</v>
@@ -5843,7 +5848,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5861,7 +5866,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5876,7 +5881,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5894,7 +5899,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5906,7 +5911,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>24</v>
@@ -5927,7 +5932,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5939,10 +5944,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5956,11 +5961,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C146" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5972,10 +5977,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5989,11 +5994,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C147" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6002,13 +6007,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6041,7 +6046,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6053,7 +6058,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>19</v>
@@ -6074,7 +6079,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6083,13 +6088,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6107,22 +6112,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6151,26 +6156,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6184,11 +6189,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6200,10 +6205,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6221,7 +6226,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6254,7 +6259,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6302,7 +6307,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6314,10 +6319,10 @@
         <v>105</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6335,7 +6340,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6347,7 +6352,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>113</v>
@@ -6368,7 +6373,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6401,7 +6406,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6410,13 +6415,13 @@
         <v>105</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6434,22 +6439,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>105</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6467,7 +6472,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6482,7 +6487,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6515,7 +6520,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6527,14 +6532,18 @@
         <v>22</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>197</v>
-      </c>
-      <c r="K165" s="7"/>
+        <v>198</v>
+      </c>
+      <c t="s" r="K165" s="7">
+        <v>248</v>
+      </c>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>63</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
@@ -6548,7 +6557,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6560,7 +6569,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>114</v>
@@ -6581,7 +6590,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6614,7 +6623,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6647,7 +6656,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6659,7 +6668,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>158</v>
@@ -6680,7 +6689,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6695,7 +6704,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6713,7 +6722,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6725,10 +6734,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6761,7 +6770,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6776,7 +6785,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6794,7 +6803,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6806,10 +6815,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6827,7 +6836,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6836,7 +6845,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>46</v>
@@ -6860,22 +6869,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6908,7 +6917,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6920,7 +6929,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>138</v>
@@ -6941,7 +6950,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6974,7 +6983,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6983,10 +6992,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>109</v>
@@ -7007,22 +7016,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7055,7 +7064,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7070,7 +7079,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7088,7 +7097,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7100,10 +7109,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7121,7 +7130,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7130,13 +7139,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7154,19 +7163,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>129</v>
@@ -7187,7 +7196,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7199,10 +7208,10 @@
         <v>105</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7220,7 +7229,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7232,10 +7241,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7268,7 +7277,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7280,7 +7289,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>115</v>
@@ -7301,7 +7310,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7313,7 +7322,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>47</v>
@@ -7349,7 +7358,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7358,13 +7367,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7382,13 +7391,13 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
@@ -7397,7 +7406,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7415,7 +7424,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7427,10 +7436,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7448,7 +7457,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7460,10 +7469,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7481,7 +7490,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7493,7 +7502,7 @@
         <v>153</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>44</v>
@@ -7529,7 +7538,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7538,13 +7547,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>143</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7562,22 +7571,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7595,7 +7604,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7607,10 +7616,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7628,7 +7637,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7640,10 +7649,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7661,7 +7670,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7676,7 +7685,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7694,7 +7703,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7706,7 +7715,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>37</v>
@@ -7727,7 +7736,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7739,7 +7748,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>122</v>
@@ -7760,7 +7769,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7772,10 +7781,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7808,7 +7817,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7817,13 +7826,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7841,19 +7850,19 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>146</v>
@@ -7874,7 +7883,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7883,7 +7892,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>88</v>
@@ -7907,13 +7916,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>32</v>
@@ -7922,7 +7931,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7940,7 +7949,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7952,10 +7961,10 @@
         <v>121</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7973,7 +7982,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7988,7 +7997,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8006,7 +8015,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8018,10 +8027,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8054,7 +8063,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8066,7 +8075,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>113</v>
@@ -8087,7 +8096,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8102,7 +8111,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8120,7 +8129,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8132,10 +8141,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8153,7 +8162,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8165,7 +8174,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>57</v>
@@ -8186,7 +8195,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8234,7 +8243,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8243,10 +8252,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>110</v>
@@ -8267,13 +8276,13 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>16</v>
@@ -8282,7 +8291,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8300,7 +8309,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8312,7 +8321,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>36</v>
@@ -8333,7 +8342,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8345,7 +8354,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>20</v>
@@ -8366,7 +8375,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8375,13 +8384,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8399,13 +8408,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
@@ -8414,7 +8423,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8432,7 +8441,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8447,7 +8456,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8465,7 +8474,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8513,7 +8522,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8525,10 +8534,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8546,7 +8555,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8555,10 +8564,10 @@
         <v>96</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>70</v>
@@ -8579,19 +8588,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>96</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>63</v>
@@ -8612,7 +8621,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8624,7 +8633,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>113</v>
@@ -8645,7 +8654,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8660,7 +8669,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8678,7 +8687,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8711,7 +8720,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8720,10 +8729,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>25</v>
@@ -8744,22 +8753,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8777,7 +8786,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8789,7 +8798,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>66</v>
@@ -8810,7 +8819,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8858,7 +8867,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8870,7 +8879,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>146</v>
@@ -8891,7 +8900,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8903,10 +8912,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8924,7 +8933,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8936,10 +8945,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8957,7 +8966,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8972,7 +8981,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8990,7 +8999,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8999,7 +9008,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>53</v>
@@ -9023,22 +9032,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9056,7 +9065,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9068,10 +9077,10 @@
         <v>125</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9104,7 +9113,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9116,7 +9125,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>62</v>
@@ -9137,7 +9146,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9152,7 +9161,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9170,7 +9179,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9203,7 +9212,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9215,10 +9224,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9236,7 +9245,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9248,10 +9257,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9269,7 +9278,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9284,7 +9293,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9302,7 +9311,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9314,7 +9323,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>66</v>
@@ -9335,7 +9344,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9383,7 +9392,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9392,13 +9401,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9416,19 +9425,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>79</v>
@@ -9449,7 +9458,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9461,10 +9470,10 @@
         <v>101</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9482,7 +9491,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9494,10 +9503,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9515,7 +9524,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9524,7 +9533,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>139</v>
@@ -9548,13 +9557,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>32</v>
@@ -9563,7 +9572,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9581,7 +9590,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9593,7 +9602,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>65</v>
@@ -9614,7 +9623,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9626,10 +9635,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9655,14 +9664,14 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>130</v>
+        <v>825</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9671,13 +9680,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9688,29 +9697,29 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>133</v>
+        <v>826</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>71</v>
+        <v>312</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9728,7 +9737,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9761,7 +9770,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9773,7 +9782,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>83</v>
@@ -9794,7 +9803,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9809,7 +9818,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9842,7 +9851,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9857,7 +9866,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9875,7 +9884,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9887,10 +9896,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9908,7 +9917,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9917,13 +9926,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9941,13 +9950,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
@@ -9974,16 +9983,16 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
+        <v>313</v>
+      </c>
+      <c r="F278" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G278" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H278" s="8">
         <v>309</v>
-      </c>
-      <c r="F278" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G278" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H278" s="8">
-        <v>307</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>155</v>
@@ -10007,22 +10016,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
+        <v>313</v>
+      </c>
+      <c r="F279" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G279" s="8">
         <v>309</v>
       </c>
-      <c r="F279" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G279" s="8">
-        <v>307</v>
-      </c>
       <c t="s" r="H279" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10040,7 +10049,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10052,7 +10061,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>99</v>
@@ -10073,7 +10082,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10085,7 +10094,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>75</v>
@@ -10121,7 +10130,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10136,7 +10145,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10154,7 +10163,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10187,7 +10196,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10199,7 +10208,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>133</v>
@@ -10235,7 +10244,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10244,13 +10253,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>135</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10268,22 +10277,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>314</v>
+        <v>248</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10301,7 +10310,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10310,10 +10319,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>51</v>
@@ -10334,19 +10343,19 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>72</v>
@@ -10367,7 +10376,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10376,13 +10385,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10400,19 +10409,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>40</v>
@@ -10433,7 +10442,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10448,7 +10457,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10466,7 +10475,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10478,10 +10487,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10514,7 +10523,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10526,7 +10535,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>30</v>
@@ -10547,7 +10556,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10562,7 +10571,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10580,7 +10589,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10595,7 +10604,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10613,7 +10622,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10625,7 +10634,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>94</v>
@@ -10646,7 +10655,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10655,7 +10664,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>37</v>
@@ -10679,13 +10688,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>32</v>
@@ -10712,7 +10721,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10727,7 +10736,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10745,7 +10754,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10793,7 +10802,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10808,7 +10817,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10826,7 +10835,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10838,10 +10847,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10859,7 +10868,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10871,10 +10880,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10892,7 +10901,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10904,10 +10913,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10925,7 +10934,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10937,7 +10946,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>41</v>
@@ -10958,7 +10967,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10970,7 +10979,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>76</v>
@@ -10999,14 +11008,14 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11015,13 +11024,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11032,49 +11041,63 @@
         <v>13</v>
       </c>
       <c r="B313" s="7">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="H313" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I313" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J313" s="7">
+        <v>36</v>
+      </c>
+      <c r="K313" s="7"/>
+      <c r="L313" s="7"/>
+      <c r="M313" s="7"/>
+    </row>
+    <row r="314" ht="14.25" customHeight="1">
+      <c t="s" r="A314" s="6">
+        <v>13</v>
+      </c>
+      <c r="B314" s="7">
+        <v>511</v>
+      </c>
+      <c t="s" r="C314" s="7">
+        <v>14</v>
+      </c>
+      <c r="D314" s="7"/>
+      <c t="s" r="E314" s="7">
+        <v>326</v>
+      </c>
+      <c r="F314" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G314" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H314" s="8">
         <v>22</v>
       </c>
-      <c t="s" r="H313" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I313" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="J313" s="7">
-        <v>72</v>
-      </c>
-      <c t="s" r="K313" s="7">
-        <v>53</v>
-      </c>
-      <c r="L313" s="7"/>
-      <c t="s" r="M313" s="7">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="314" ht="14.25" customHeight="1">
-      <c r="A314" s="6"/>
-      <c r="B314" s="7"/>
-      <c r="C314" s="7"/>
-      <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7"/>
-      <c r="G314" s="8"/>
-      <c r="H314" s="8"/>
-      <c r="I314" s="7"/>
-      <c r="J314" s="7"/>
+      <c t="s" r="I314" s="7">
+        <v>155</v>
+      </c>
+      <c t="s" r="J314" s="7">
+        <v>284</v>
+      </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
@@ -11084,63 +11107,49 @@
         <v>13</v>
       </c>
       <c r="B315" s="7">
-        <v>809</v>
+        <v>510</v>
       </c>
       <c t="s" r="C315" s="7">
         <v>14</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>221</v>
-      </c>
-      <c r="K315" s="7"/>
+        <v>72</v>
+      </c>
+      <c t="s" r="K315" s="7">
+        <v>53</v>
+      </c>
       <c r="L315" s="7"/>
-      <c r="M315" s="7"/>
+      <c t="s" r="M315" s="7">
+        <v>140</v>
+      </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
-      <c t="s" r="A316" s="6">
-        <v>13</v>
-      </c>
-      <c r="B316" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C316" s="7">
-        <v>14</v>
-      </c>
+      <c r="A316" s="6"/>
+      <c r="B316" s="7"/>
+      <c r="C316" s="7"/>
       <c r="D316" s="7"/>
-      <c t="s" r="E316" s="7">
-        <v>325</v>
-      </c>
-      <c r="F316" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G316" s="8">
-        <v>326</v>
-      </c>
-      <c t="s" r="H316" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I316" s="7">
-        <v>224</v>
-      </c>
-      <c t="s" r="J316" s="7">
-        <v>174</v>
-      </c>
+      <c r="E316" s="7"/>
+      <c r="F316" s="7"/>
+      <c r="G316" s="8"/>
+      <c r="H316" s="8"/>
+      <c r="I316" s="7"/>
+      <c r="J316" s="7"/>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c r="M316" s="7"/>
@@ -11150,14 +11159,14 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>640</v>
+        <v>809</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11166,13 +11175,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>22</v>
+        <v>328</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>316</v>
+        <v>146</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11183,29 +11192,29 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>639</v>
+        <v>808</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>22</v>
+        <v>328</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>327</v>
+        <v>225</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>328</v>
+        <v>175</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11216,14 +11225,14 @@
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>822</v>
+        <v>640</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11232,29 +11241,47 @@
         <v>32</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>169</v>
+        <v>319</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="6"/>
-      <c r="B320" s="7"/>
-      <c r="C320" s="7"/>
+      <c t="s" r="A320" s="6">
+        <v>13</v>
+      </c>
+      <c r="B320" s="7">
+        <v>639</v>
+      </c>
+      <c t="s" r="C320" s="7">
+        <v>14</v>
+      </c>
       <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
-      <c r="G320" s="8"/>
-      <c r="H320" s="8"/>
-      <c r="I320" s="7"/>
-      <c r="J320" s="7"/>
+      <c t="s" r="E320" s="7">
+        <v>327</v>
+      </c>
+      <c r="F320" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G320" s="8">
+        <v>22</v>
+      </c>
+      <c t="s" r="H320" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="I320" s="7">
+        <v>329</v>
+      </c>
+      <c t="s" r="J320" s="7">
+        <v>330</v>
+      </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c r="M320" s="7"/>
@@ -11264,63 +11291,45 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>431</v>
+        <v>822</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F321" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>330</v>
+        <v>170</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c t="s" r="A322" s="6">
-        <v>13</v>
-      </c>
-      <c r="B322" s="7">
-        <v>430</v>
-      </c>
-      <c t="s" r="C322" s="7">
-        <v>14</v>
-      </c>
+      <c r="A322" s="6"/>
+      <c r="B322" s="7"/>
+      <c r="C322" s="7"/>
       <c r="D322" s="7"/>
-      <c t="s" r="E322" s="7">
-        <v>329</v>
-      </c>
-      <c r="F322" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G322" s="8">
-        <v>173</v>
-      </c>
-      <c t="s" r="H322" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I322" s="7">
-        <v>62</v>
-      </c>
-      <c t="s" r="J322" s="7">
-        <v>231</v>
-      </c>
+      <c r="E322" s="7"/>
+      <c r="F322" s="7"/>
+      <c r="G322" s="8"/>
+      <c r="H322" s="8"/>
+      <c r="I322" s="7"/>
+      <c r="J322" s="7"/>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
@@ -11330,14 +11339,14 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11346,13 +11355,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>88</v>
+        <v>332</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>331</v>
+        <v>197</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11363,29 +11372,29 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>322</v>
+        <v>232</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11396,14 +11405,14 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>913</v>
+        <v>403</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11412,13 +11421,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>332</v>
+        <v>205</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11429,45 +11438,63 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>914</v>
+        <v>404</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>332</v>
+        <v>205</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>141</v>
+        <v>312</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c r="M326" s="7"/>
     </row>
     <row r="327" ht="14.25" customHeight="1">
-      <c r="A327" s="6"/>
-      <c r="B327" s="7"/>
-      <c r="C327" s="7"/>
+      <c t="s" r="A327" s="6">
+        <v>13</v>
+      </c>
+      <c r="B327" s="7">
+        <v>913</v>
+      </c>
+      <c t="s" r="C327" s="7">
+        <v>14</v>
+      </c>
       <c r="D327" s="7"/>
-      <c r="E327" s="7"/>
-      <c r="F327" s="7"/>
-      <c r="G327" s="8"/>
-      <c r="H327" s="8"/>
-      <c r="I327" s="7"/>
-      <c r="J327" s="7"/>
+      <c t="s" r="E327" s="7">
+        <v>331</v>
+      </c>
+      <c r="F327" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G327" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H327" s="8">
+        <v>334</v>
+      </c>
+      <c t="s" r="I327" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J327" s="7">
+        <v>106</v>
+      </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c r="M327" s="7"/>
@@ -11477,63 +11504,45 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>628</v>
+        <v>914</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>32</v>
+        <v>334</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c r="M328" s="7"/>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c t="s" r="A329" s="6">
-        <v>13</v>
-      </c>
-      <c r="B329" s="7">
-        <v>720</v>
-      </c>
-      <c t="s" r="C329" s="7">
-        <v>14</v>
-      </c>
+      <c r="A329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="7"/>
       <c r="D329" s="7"/>
-      <c t="s" r="E329" s="7">
-        <v>333</v>
-      </c>
-      <c r="F329" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G329" s="8">
-        <v>22</v>
-      </c>
-      <c t="s" r="H329" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="I329" s="7">
-        <v>79</v>
-      </c>
-      <c t="s" r="J329" s="7">
-        <v>276</v>
-      </c>
+      <c r="E329" s="7"/>
+      <c r="F329" s="7"/>
+      <c r="G329" s="8"/>
+      <c r="H329" s="8"/>
+      <c r="I329" s="7"/>
+      <c r="J329" s="7"/>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c r="M329" s="7"/>
@@ -11543,29 +11552,29 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>721</v>
+        <v>628</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11576,14 +11585,14 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11592,13 +11601,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11609,29 +11618,29 @@
         <v>13</v>
       </c>
       <c r="B332" s="7">
-        <v>480</v>
+        <v>721</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H332" s="8">
+        <v>22</v>
+      </c>
+      <c t="s" r="I332" s="7">
         <v>199</v>
       </c>
-      <c t="s" r="H332" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I332" s="7">
-        <v>269</v>
-      </c>
       <c t="s" r="J332" s="7">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11642,29 +11651,29 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>481</v>
+        <v>703</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>39</v>
+        <v>338</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11675,45 +11684,63 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>704</v>
+        <v>480</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c r="M334" s="7"/>
     </row>
     <row r="335" ht="15" customHeight="1">
-      <c r="A335" s="6"/>
-      <c r="B335" s="7"/>
-      <c r="C335" s="7"/>
+      <c t="s" r="A335" s="6">
+        <v>13</v>
+      </c>
+      <c r="B335" s="7">
+        <v>481</v>
+      </c>
+      <c t="s" r="C335" s="7">
+        <v>14</v>
+      </c>
       <c r="D335" s="7"/>
-      <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
-      <c r="G335" s="8"/>
-      <c r="H335" s="8"/>
-      <c r="I335" s="7"/>
-      <c r="J335" s="7"/>
+      <c t="s" r="E335" s="7">
+        <v>335</v>
+      </c>
+      <c r="F335" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G335" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H335" s="8">
+        <v>200</v>
+      </c>
+      <c t="s" r="I335" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J335" s="7">
+        <v>122</v>
+      </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c r="M335" s="7"/>
@@ -11723,63 +11750,45 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>270</v>
+        <v>704</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F336" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c r="M336" s="7"/>
     </row>
     <row r="337" ht="14.25" customHeight="1">
-      <c t="s" r="A337" s="6">
-        <v>13</v>
-      </c>
-      <c r="B337" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="C337" s="7">
-        <v>14</v>
-      </c>
+      <c r="A337" s="6"/>
+      <c r="B337" s="7"/>
+      <c r="C337" s="7"/>
       <c r="D337" s="7"/>
-      <c t="s" r="E337" s="7">
-        <v>338</v>
-      </c>
-      <c r="F337" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G337" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="H337" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I337" s="7">
-        <v>133</v>
-      </c>
-      <c t="s" r="J337" s="7">
-        <v>209</v>
-      </c>
+      <c r="E337" s="7"/>
+      <c r="F337" s="7"/>
+      <c r="G337" s="8"/>
+      <c r="H337" s="8"/>
+      <c r="I337" s="7"/>
+      <c r="J337" s="7"/>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c r="M337" s="7"/>
@@ -11789,14 +11798,14 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11805,13 +11814,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11822,29 +11831,29 @@
         <v>13</v>
       </c>
       <c r="B339" s="7">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c t="s" r="C339" s="7">
         <v>14</v>
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11855,14 +11864,14 @@
         <v>13</v>
       </c>
       <c r="B340" s="7">
-        <v>312</v>
+        <v>136</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11871,13 +11880,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>54</v>
+        <v>340</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11888,45 +11897,63 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>311</v>
+        <v>145</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>158</v>
+        <v>341</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>41</v>
+        <v>342</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
-      <c r="C342" s="7"/>
+      <c t="s" r="A342" s="6">
+        <v>13</v>
+      </c>
+      <c r="B342" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="C342" s="7">
+        <v>14</v>
+      </c>
       <c r="D342" s="7"/>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
-      <c r="I342" s="7"/>
-      <c r="J342" s="7"/>
+      <c t="s" r="E342" s="7">
+        <v>339</v>
+      </c>
+      <c r="F342" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G342" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H342" s="8">
+        <v>172</v>
+      </c>
+      <c t="s" r="I342" s="7">
+        <v>54</v>
+      </c>
+      <c t="s" r="J342" s="7">
+        <v>177</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c r="M342" s="7"/>
@@ -11936,63 +11963,45 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>421</v>
+        <v>311</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F343" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>307</v>
+        <v>32</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c t="s" r="A344" s="6">
-        <v>13</v>
-      </c>
-      <c r="B344" s="7">
-        <v>422</v>
-      </c>
-      <c t="s" r="C344" s="7">
-        <v>14</v>
-      </c>
+      <c r="A344" s="6"/>
+      <c r="B344" s="7"/>
+      <c r="C344" s="7"/>
       <c r="D344" s="7"/>
-      <c t="s" r="E344" s="7">
-        <v>342</v>
-      </c>
-      <c r="F344" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G344" s="8">
-        <v>307</v>
-      </c>
-      <c t="s" r="H344" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I344" s="7">
-        <v>300</v>
-      </c>
-      <c t="s" r="J344" s="7">
-        <v>276</v>
-      </c>
+      <c r="E344" s="7"/>
+      <c r="F344" s="7"/>
+      <c r="G344" s="8"/>
+      <c r="H344" s="8"/>
+      <c r="I344" s="7"/>
+      <c r="J344" s="7"/>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
@@ -12002,14 +12011,14 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12018,13 +12027,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>64</v>
+        <v>309</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>343</v>
+        <v>30</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>344</v>
+        <v>70</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12035,29 +12044,29 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>64</v>
+        <v>309</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>72</v>
+        <v>302</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>345</v>
+        <v>278</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12068,14 +12077,14 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12084,13 +12093,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>298</v>
+        <v>64</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>40</v>
+        <v>345</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12101,45 +12110,63 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>298</v>
+        <v>64</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>227</v>
+        <v>346</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
     </row>
     <row r="349" ht="14.25" customHeight="1">
-      <c r="A349" s="6"/>
-      <c r="B349" s="7"/>
-      <c r="C349" s="7"/>
+      <c t="s" r="A349" s="6">
+        <v>13</v>
+      </c>
+      <c r="B349" s="7">
+        <v>495</v>
+      </c>
+      <c t="s" r="C349" s="7">
+        <v>14</v>
+      </c>
       <c r="D349" s="7"/>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
-      <c r="G349" s="8"/>
-      <c r="H349" s="8"/>
-      <c r="I349" s="7"/>
-      <c r="J349" s="7"/>
+      <c t="s" r="E349" s="7">
+        <v>343</v>
+      </c>
+      <c r="F349" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G349" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H349" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="I349" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="J349" s="7">
+        <v>40</v>
+      </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c r="M349" s="7"/>
@@ -12149,63 +12176,45 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>1362</v>
+        <v>496</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F350" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>254</v>
+        <v>25</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>334</v>
+        <v>228</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c r="M350" s="7"/>
     </row>
     <row r="351" ht="14.25" customHeight="1">
-      <c t="s" r="A351" s="6">
-        <v>13</v>
-      </c>
-      <c r="B351" s="7">
-        <v>1363</v>
-      </c>
-      <c t="s" r="C351" s="7">
-        <v>14</v>
-      </c>
+      <c r="A351" s="6"/>
+      <c r="B351" s="7"/>
+      <c r="C351" s="7"/>
       <c r="D351" s="7"/>
-      <c t="s" r="E351" s="7">
-        <v>346</v>
-      </c>
-      <c r="F351" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G351" s="8">
-        <v>204</v>
-      </c>
-      <c t="s" r="H351" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I351" s="7">
-        <v>164</v>
-      </c>
-      <c t="s" r="J351" s="7">
-        <v>86</v>
-      </c>
+      <c r="E351" s="7"/>
+      <c r="F351" s="7"/>
+      <c r="G351" s="8"/>
+      <c r="H351" s="8"/>
+      <c r="I351" s="7"/>
+      <c r="J351" s="7"/>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
@@ -12215,14 +12224,14 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>272</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12231,13 +12240,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12248,29 +12257,29 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>7078</v>
+        <v>1363</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>347</v>
+        <v>32</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>348</v>
+        <v>86</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12281,29 +12290,29 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>7079</v>
+        <v>272</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>347</v>
+        <v>32</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>105</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>341</v>
+        <v>192</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12314,14 +12323,14 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>273</v>
+        <v>7078</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12330,13 +12339,13 @@
         <v>105</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>32</v>
+        <v>348</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>55</v>
+        <v>349</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12347,29 +12356,29 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>3908</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>32</v>
+        <v>348</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>318</v>
+        <v>176</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12377,114 +12386,114 @@
     </row>
     <row r="357" ht="14.25" customHeight="1">
       <c t="s" r="A357" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>3909</v>
+        <v>273</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>350</v>
+        <v>23</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>351</v>
+        <v>55</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c r="M357" s="7"/>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
+      <c t="s" r="A358" s="6">
+        <v>13</v>
+      </c>
+      <c r="B358" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C358" s="7">
+        <v>14</v>
+      </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="8"/>
-      <c r="H358" s="8"/>
-      <c r="I358" s="7"/>
-      <c r="J358" s="7"/>
+      <c t="s" r="E358" s="7">
+        <v>347</v>
+      </c>
+      <c r="F358" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G358" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H358" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I358" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="J358" s="7">
+        <v>350</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B359" s="7">
-        <v>125</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
+        <v>347</v>
+      </c>
+      <c r="F359" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G359" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H359" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="I359" s="7">
+        <v>351</v>
+      </c>
+      <c t="s" r="J359" s="7">
         <v>352</v>
-      </c>
-      <c r="F359" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G359" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H359" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I359" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J359" s="7">
-        <v>275</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c t="s" r="A360" s="6">
-        <v>13</v>
-      </c>
-      <c r="B360" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="C360" s="7">
-        <v>14</v>
-      </c>
+      <c r="A360" s="6"/>
+      <c r="B360" s="7"/>
+      <c r="C360" s="7"/>
       <c r="D360" s="7"/>
-      <c t="s" r="E360" s="7">
-        <v>352</v>
-      </c>
-      <c r="F360" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G360" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H360" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I360" s="7">
-        <v>80</v>
-      </c>
-      <c t="s" r="J360" s="7">
-        <v>281</v>
-      </c>
+      <c r="E360" s="7"/>
+      <c r="F360" s="7"/>
+      <c r="G360" s="8"/>
+      <c r="H360" s="8"/>
+      <c r="I360" s="7"/>
+      <c r="J360" s="7"/>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c r="M360" s="7"/>
@@ -12494,14 +12503,14 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12513,10 +12522,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12527,14 +12536,14 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12546,10 +12555,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>130</v>
+        <v>283</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12560,14 +12569,14 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12579,26 +12588,44 @@
         <v>32</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>353</v>
+        <v>104</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c r="A364" s="6"/>
-      <c r="B364" s="7"/>
-      <c r="C364" s="7"/>
+      <c t="s" r="A364" s="6">
+        <v>13</v>
+      </c>
+      <c r="B364" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="C364" s="7">
+        <v>14</v>
+      </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
-      <c r="G364" s="8"/>
-      <c r="H364" s="8"/>
-      <c r="I364" s="7"/>
-      <c r="J364" s="7"/>
+      <c t="s" r="E364" s="7">
+        <v>353</v>
+      </c>
+      <c r="F364" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G364" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H364" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I364" s="7">
+        <v>181</v>
+      </c>
+      <c t="s" r="J364" s="7">
+        <v>130</v>
+      </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
@@ -12608,14 +12635,14 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>771</v>
+        <v>163</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12624,47 +12651,29 @@
         <v>16</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c t="s" r="A366" s="6">
-        <v>13</v>
-      </c>
-      <c r="B366" s="7">
-        <v>770</v>
-      </c>
-      <c t="s" r="C366" s="7">
-        <v>14</v>
-      </c>
+      <c r="A366" s="6"/>
+      <c r="B366" s="7"/>
+      <c r="C366" s="7"/>
       <c r="D366" s="7"/>
-      <c t="s" r="E366" s="7">
-        <v>354</v>
-      </c>
-      <c r="F366" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G366" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H366" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I366" s="7">
-        <v>267</v>
-      </c>
-      <c t="s" r="J366" s="7">
-        <v>242</v>
-      </c>
+      <c r="E366" s="7"/>
+      <c r="F366" s="7"/>
+      <c r="G366" s="8"/>
+      <c r="H366" s="8"/>
+      <c r="I366" s="7"/>
+      <c r="J366" s="7"/>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
@@ -12674,14 +12683,14 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>463</v>
+        <v>771</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12690,13 +12699,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12707,29 +12716,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>464</v>
+        <v>770</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12740,14 +12749,14 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>1511</v>
+        <v>143</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12756,13 +12765,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>356</v>
+        <v>293</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12773,29 +12782,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>1518</v>
+        <v>146</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>243</v>
+        <v>346</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>25</v>
+        <v>295</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12813,7 +12822,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12825,7 +12834,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>357</v>
@@ -12846,7 +12855,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12861,7 +12870,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12939,7 +12948,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>35</v>
@@ -12969,13 +12978,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12999,16 +13008,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13053,10 +13062,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13083,13 +13092,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13113,16 +13122,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13149,7 +13158,7 @@
         <v>22</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>115</v>
@@ -13179,16 +13188,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13221,7 +13230,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13230,10 +13239,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>34</v>
@@ -13254,22 +13263,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13287,7 +13296,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13299,10 +13308,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13320,7 +13329,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13332,10 +13341,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13353,7 +13362,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13368,7 +13377,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13386,7 +13395,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13401,7 +13410,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13419,7 +13428,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13431,7 +13440,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>58</v>
@@ -13467,7 +13476,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13479,7 +13488,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>146</v>
@@ -13500,7 +13509,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13515,7 +13524,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13533,7 +13542,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13542,13 +13551,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13566,13 +13575,13 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>32</v>
@@ -13581,7 +13590,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13599,7 +13608,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13608,10 +13617,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>156</v>
@@ -13632,13 +13641,13 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>32</v>
@@ -13647,7 +13656,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13665,7 +13674,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13677,10 +13686,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13698,7 +13707,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13713,7 +13722,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13746,7 +13755,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13755,7 +13764,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>77</v>
@@ -13779,13 +13788,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>32</v>
@@ -13794,7 +13803,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13812,7 +13821,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13821,10 +13830,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>128</v>
@@ -13845,13 +13854,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>32</v>
@@ -13878,7 +13887,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13890,7 +13899,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>140</v>
@@ -13911,7 +13920,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13923,10 +13932,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13944,7 +13953,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13959,7 +13968,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13977,7 +13986,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13989,10 +13998,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14025,7 +14034,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14034,7 +14043,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>85</v>
@@ -14058,13 +14067,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>32</v>
@@ -14091,7 +14100,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14100,7 +14109,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>50</v>
@@ -14124,19 +14133,19 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>35</v>
@@ -14157,7 +14166,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14166,7 +14175,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>93</v>
@@ -14190,19 +14199,19 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>82</v>
@@ -14223,7 +14232,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14232,13 +14241,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14256,19 +14265,19 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>357</v>
@@ -14304,7 +14313,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14313,13 +14322,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14337,22 +14346,22 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14363,14 +14372,14 @@
         <v>13</v>
       </c>
       <c r="B422" s="7">
-        <v>362</v>
+        <v>278</v>
       </c>
       <c t="s" r="C422" s="7">
         <v>14</v>
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14379,13 +14388,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>72</v>
+        <v>345</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14396,111 +14405,111 @@
         <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>363</v>
+        <v>279</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>175</v>
+        <v>284</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c r="M423" s="7"/>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c t="s" r="A424" s="6">
-        <v>13</v>
-      </c>
-      <c r="B424" s="7">
-        <v>3948</v>
-      </c>
-      <c t="s" r="C424" s="7">
-        <v>14</v>
-      </c>
+      <c r="A424" s="6"/>
+      <c r="B424" s="7"/>
+      <c r="C424" s="7"/>
       <c r="D424" s="7"/>
-      <c t="s" r="E424" s="7">
-        <v>371</v>
-      </c>
-      <c r="F424" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G424" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H424" s="8">
-        <v>157</v>
-      </c>
-      <c t="s" r="I424" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="J424" s="7">
-        <v>235</v>
-      </c>
+      <c r="E424" s="7"/>
+      <c r="F424" s="7"/>
+      <c r="G424" s="8"/>
+      <c r="H424" s="8"/>
+      <c r="I424" s="7"/>
+      <c r="J424" s="7"/>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c r="M424" s="7"/>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B425" s="7">
-        <v>3949</v>
+        <v>724</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F425" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c r="M425" s="7"/>
     </row>
     <row r="426" ht="14.25" customHeight="1">
-      <c r="A426" s="6"/>
-      <c r="B426" s="7"/>
-      <c r="C426" s="7"/>
+      <c t="s" r="A426" s="6">
+        <v>13</v>
+      </c>
+      <c r="B426" s="7">
+        <v>725</v>
+      </c>
+      <c t="s" r="C426" s="7">
+        <v>14</v>
+      </c>
       <c r="D426" s="7"/>
-      <c r="E426" s="7"/>
-      <c r="F426" s="7"/>
-      <c r="G426" s="8"/>
-      <c r="H426" s="8"/>
-      <c r="I426" s="7"/>
-      <c r="J426" s="7"/>
+      <c t="s" r="E426" s="7">
+        <v>373</v>
+      </c>
+      <c r="F426" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G426" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H426" s="8">
+        <v>22</v>
+      </c>
+      <c t="s" r="I426" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J426" s="7">
+        <v>277</v>
+      </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c r="M426" s="7"/>
@@ -14510,14 +14519,14 @@
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>724</v>
+        <v>701</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14526,13 +14535,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14543,29 +14552,29 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>44</v>
+        <v>344</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>275</v>
+        <v>102</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14576,14 +14585,14 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>701</v>
+        <v>8510</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14592,13 +14601,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>287</v>
+        <v>54</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14609,63 +14618,45 @@
         <v>13</v>
       </c>
       <c r="B430" s="7">
-        <v>702</v>
+        <v>8511</v>
       </c>
       <c t="s" r="C430" s="7">
         <v>14</v>
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c r="M430" s="7"/>
     </row>
     <row r="431" ht="14.25" customHeight="1">
-      <c t="s" r="A431" s="6">
-        <v>13</v>
-      </c>
-      <c r="B431" s="7">
-        <v>8510</v>
-      </c>
-      <c t="s" r="C431" s="7">
-        <v>14</v>
-      </c>
+      <c r="A431" s="6"/>
+      <c r="B431" s="7"/>
+      <c r="C431" s="7"/>
       <c r="D431" s="7"/>
-      <c t="s" r="E431" s="7">
-        <v>372</v>
-      </c>
-      <c r="F431" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G431" s="8">
-        <v>22</v>
-      </c>
-      <c t="s" r="H431" s="8">
-        <v>52</v>
-      </c>
-      <c t="s" r="I431" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="J431" s="7">
-        <v>54</v>
-      </c>
+      <c r="E431" s="7"/>
+      <c r="F431" s="7"/>
+      <c r="G431" s="8"/>
+      <c r="H431" s="8"/>
+      <c r="I431" s="7"/>
+      <c r="J431" s="7"/>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
@@ -14675,45 +14666,63 @@
         <v>13</v>
       </c>
       <c r="B432" s="7">
-        <v>8511</v>
+        <v>123</v>
       </c>
       <c t="s" r="C432" s="7">
         <v>14</v>
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F432" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>129</v>
+        <v>281</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c r="M432" s="7"/>
     </row>
     <row r="433" ht="14.25" customHeight="1">
-      <c r="A433" s="6"/>
-      <c r="B433" s="7"/>
-      <c r="C433" s="7"/>
+      <c t="s" r="A433" s="6">
+        <v>13</v>
+      </c>
+      <c r="B433" s="7">
+        <v>801</v>
+      </c>
+      <c t="s" r="C433" s="7">
+        <v>14</v>
+      </c>
       <c r="D433" s="7"/>
-      <c r="E433" s="7"/>
-      <c r="F433" s="7"/>
-      <c r="G433" s="8"/>
-      <c r="H433" s="8"/>
-      <c r="I433" s="7"/>
-      <c r="J433" s="7"/>
+      <c t="s" r="E433" s="7">
+        <v>374</v>
+      </c>
+      <c r="F433" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G433" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H433" s="8">
+        <v>101</v>
+      </c>
+      <c t="s" r="I433" s="7">
+        <v>375</v>
+      </c>
+      <c t="s" r="J433" s="7">
+        <v>167</v>
+      </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c r="M433" s="7"/>
@@ -14723,29 +14732,29 @@
         <v>13</v>
       </c>
       <c r="B434" s="7">
-        <v>123</v>
+        <v>802</v>
       </c>
       <c t="s" r="C434" s="7">
         <v>14</v>
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14756,14 +14765,14 @@
         <v>13</v>
       </c>
       <c r="B435" s="7">
-        <v>801</v>
+        <v>362</v>
       </c>
       <c t="s" r="C435" s="7">
         <v>14</v>
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -14772,13 +14781,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>374</v>
+        <v>72</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14789,29 +14798,29 @@
         <v>13</v>
       </c>
       <c r="B436" s="7">
-        <v>802</v>
+        <v>363</v>
       </c>
       <c t="s" r="C436" s="7">
         <v>14</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>310</v>
+        <v>176</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>113</v>
+        <v>213</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14822,14 +14831,14 @@
         <v>13</v>
       </c>
       <c r="B437" s="7">
-        <v>278</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C437" s="7">
         <v>14</v>
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -14838,13 +14847,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14852,32 +14861,32 @@
     </row>
     <row r="438" ht="14.25" customHeight="1">
       <c t="s" r="A438" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B438" s="7">
-        <v>279</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C438" s="7">
         <v>14</v>
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14910,7 +14919,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -14925,7 +14934,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14943,7 +14952,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -14955,10 +14964,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14976,7 +14985,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -14988,7 +14997,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>71</v>
@@ -15009,7 +15018,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15021,7 +15030,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>148</v>
@@ -15042,7 +15051,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15075,7 +15084,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15090,7 +15099,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15123,7 +15132,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15156,7 +15165,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15168,7 +15177,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>51</v>
@@ -15189,7 +15198,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15222,7 +15231,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15237,7 +15246,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15255,7 +15264,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15264,10 +15273,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>59</v>
@@ -15288,22 +15297,22 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15336,7 +15345,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
@@ -15348,10 +15357,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15362,14 +15371,14 @@
         <v>13</v>
       </c>
       <c r="B455" s="7">
-        <v>825</v>
+        <v>130</v>
       </c>
       <c t="s" r="C455" s="7">
         <v>14</v>
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -15378,13 +15387,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>336</v>
+        <v>278</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15395,29 +15404,29 @@
         <v>13</v>
       </c>
       <c r="B456" s="7">
-        <v>826</v>
+        <v>133</v>
       </c>
       <c t="s" r="C456" s="7">
         <v>14</v>
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F456" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I456" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J456" s="7">
         <v>71</v>
-      </c>
-      <c t="s" r="J456" s="7">
-        <v>322</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15435,7 +15444,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -15444,10 +15453,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>82</v>
@@ -15468,13 +15477,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>32</v>
@@ -15483,7 +15492,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15516,7 +15525,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -15528,10 +15537,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15549,7 +15558,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
@@ -15561,7 +15570,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>128</v>
@@ -15582,7 +15591,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
@@ -15591,7 +15600,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I462" s="7">
         <v>93</v>
@@ -15615,13 +15624,13 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>16</v>
@@ -15630,7 +15639,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15648,7 +15657,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -15660,10 +15669,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15681,7 +15690,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -15693,10 +15702,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15729,7 +15738,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -15762,7 +15771,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -15774,7 +15783,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>90</v>
@@ -15795,7 +15804,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -15807,7 +15816,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>103</v>
@@ -15828,7 +15837,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -15840,10 +15849,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15869,14 +15878,14 @@
         <v>13</v>
       </c>
       <c r="B472" s="7">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c t="s" r="C472" s="7">
         <v>14</v>
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -15885,13 +15894,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15902,29 +15911,29 @@
         <v>13</v>
       </c>
       <c r="B473" s="7">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c t="s" r="C473" s="7">
         <v>14</v>
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -15935,14 +15944,14 @@
         <v>13</v>
       </c>
       <c r="B474" s="7">
-        <v>143</v>
+        <v>1511</v>
       </c>
       <c t="s" r="C474" s="7">
         <v>14</v>
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F474" s="7">
         <v>320</v>
@@ -15951,13 +15960,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H474" s="8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>291</v>
+        <v>360</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15968,29 +15977,29 @@
         <v>13</v>
       </c>
       <c r="B475" s="7">
-        <v>146</v>
+        <v>1518</v>
       </c>
       <c t="s" r="C475" s="7">
         <v>14</v>
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F475" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>293</v>
+        <v>25</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16023,7 +16032,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
@@ -16038,7 +16047,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16056,7 +16065,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -16068,10 +16077,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16089,7 +16098,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -16101,7 +16110,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="J479" s="7">
         <v>136</v>
@@ -16137,22 +16146,22 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
+        <v>391</v>
+      </c>
+      <c r="F481" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G481" s="8">
+        <v>392</v>
+      </c>
+      <c t="s" r="H481" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I481" s="7">
+        <v>393</v>
+      </c>
+      <c t="s" r="J481" s="7">
         <v>390</v>
-      </c>
-      <c r="F481" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G481" s="8">
-        <v>391</v>
-      </c>
-      <c t="s" r="H481" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I481" s="7">
-        <v>392</v>
-      </c>
-      <c t="s" r="J481" s="7">
-        <v>389</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16185,7 +16194,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -16218,7 +16227,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
@@ -16230,10 +16239,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16251,7 +16260,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F485" s="7">
         <v>321</v>
@@ -16263,10 +16272,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I485" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
@@ -16284,7 +16293,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -16296,7 +16305,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>25</v>
@@ -16332,7 +16341,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F488" s="7">
         <v>320</v>
@@ -16341,7 +16350,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H488" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I488" s="7">
         <v>144</v>
@@ -16365,13 +16374,13 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F489" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G489" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H489" s="8">
         <v>96</v>
@@ -16398,7 +16407,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F490" s="7">
         <v>320</v>
@@ -16407,10 +16416,10 @@
         <v>96</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J490" s="7">
         <v>80</v>
@@ -16431,13 +16440,13 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F491" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>16</v>
@@ -16464,7 +16473,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F492" s="7">
         <v>320</v>
@@ -16476,7 +16485,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I492" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J492" s="7">
         <v>82</v>
@@ -16497,7 +16506,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F493" s="7">
         <v>320</v>
@@ -16509,10 +16518,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -16530,7 +16539,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F494" s="7">
         <v>320</v>
@@ -16542,10 +16551,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J494" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
@@ -16578,7 +16587,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F496" s="7">
         <v>330</v>
@@ -16587,13 +16596,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H496" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I496" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -16611,13 +16620,13 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F497" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G497" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H497" s="8">
         <v>17</v>
@@ -16626,7 +16635,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J497" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
@@ -16659,22 +16668,22 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F499" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G499" s="8">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c t="s" r="H499" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I499" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J499" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
@@ -16707,22 +16716,22 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F501" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G501" s="8">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="H501" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I501" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J501" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
@@ -16740,7 +16749,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F502" s="7">
         <v>330</v>
@@ -16752,7 +16761,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I502" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J502" s="7">
         <v>41</v>
@@ -16784,11 +16793,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C504" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F504" s="7">
         <v>330</v>
@@ -16797,7 +16806,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H504" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I504" s="7">
         <v>87</v>
@@ -16817,23 +16826,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C505" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F505" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G505" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="H505" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I505" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J505" s="7">
         <v>67</v>
@@ -16869,7 +16878,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F507" s="7">
         <v>330</v>
@@ -16878,10 +16887,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H507" s="8">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="I507" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J507" s="7">
         <v>107</v>
@@ -16902,22 +16911,22 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F508" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G508" s="8">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="H508" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I508" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J508" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
@@ -16950,7 +16959,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F510" s="7">
         <v>330</v>
@@ -16965,7 +16974,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J510" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
@@ -16983,7 +16992,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F511" s="7">
         <v>330</v>
@@ -16992,13 +17001,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H511" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J511" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
@@ -17016,19 +17025,19 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F512" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G512" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="H512" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I512" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J512" s="7">
         <v>70</v>
@@ -17064,7 +17073,7 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F514" s="7">
         <v>330</v>
@@ -17073,13 +17082,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H514" s="8">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="I514" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J514" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
@@ -17097,22 +17106,22 @@
       </c>
       <c r="D515" s="7"/>
       <c t="s" r="E515" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F515" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G515" s="8">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="H515" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I515" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c t="s" r="J515" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
@@ -17120,7 +17129,7 @@
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c t="s" r="A516" s="9">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B516" s="9"/>
       <c r="C516" s="9"/>
@@ -17140,7 +17149,7 @@
     <row r="517" ht="65.25" customHeight="1"/>
     <row r="518" ht="16.5" customHeight="1">
       <c t="s" r="A518" s="10">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B518" s="10"/>
       <c r="C518" s="10"/>
@@ -17153,7 +17162,7 @@
       <c r="J518" s="10"/>
       <c r="K518" s="10"/>
       <c t="s" r="L518" s="11">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M518" s="11"/>
       <c r="N518" s="11"/>

--- a/Data/FlightPlan/FPL_28AUG26.xlsx
+++ b/Data/FlightPlan/FPL_28AUG26.xlsx
@@ -1229,6 +1229,9 @@
     <t>15:00</t>
   </si>
   <si>
+    <t>14:58</t>
+  </si>
+  <si>
     <t>01:30</t>
   </si>
   <si>
@@ -1268,9 +1271,6 @@
     <t>10:02</t>
   </si>
   <si>
-    <t>14:47</t>
-  </si>
-  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1409,6 +1409,9 @@
     <t>VN-A689</t>
   </si>
   <si>
+    <t>14:52</t>
+  </si>
+  <si>
     <t>SAI</t>
   </si>
   <si>
@@ -1523,7 +1526,7 @@
     <t>Total Record(s): 426</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 28, 2026 12:33</t>
+    <t xml:space="preserve">Generated on  Aug 28, 2026 12:40</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6370,9 +6373,13 @@
       <c t="s" r="J148" s="7">
         <v>56</v>
       </c>
-      <c r="K148" s="7"/>
+      <c t="s" r="K148" s="7">
+        <v>149</v>
+      </c>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>221</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
@@ -12793,7 +12800,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12889,7 +12896,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12919,10 +12926,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12955,7 +12962,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12990,7 +12997,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13023,7 +13030,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13056,7 +13063,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13068,7 +13075,7 @@
         <v>301</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>158</v>
@@ -13089,7 +13096,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13137,7 +13144,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13149,7 +13156,7 @@
         <v>178</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>166</v>
@@ -13157,7 +13164,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13172,7 +13179,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13192,7 +13199,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13207,7 +13214,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13240,7 +13247,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13273,7 +13280,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13306,7 +13313,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13354,7 +13361,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13389,7 +13396,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13409,7 +13416,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13424,7 +13431,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13457,7 +13464,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13505,7 +13512,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13525,7 +13532,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13540,7 +13547,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13560,7 +13567,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>419</v>
+        <v>406</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13575,7 +13582,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13590,7 +13597,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13608,7 +13615,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13641,7 +13648,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -15520,7 +15527,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>238</v>
@@ -16412,7 +16419,9 @@
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
-      <c r="M470" s="7"/>
+      <c t="s" r="M470" s="7">
+        <v>466</v>
+      </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
       <c t="s" r="A471" s="6">
@@ -16435,7 +16444,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c t="s" r="I471" s="7">
         <v>57</v>
@@ -16465,7 +16474,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c t="s" r="H472" s="8">
         <v>29</v>
@@ -16507,7 +16516,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -16527,7 +16536,7 @@
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -16542,7 +16551,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -16577,7 +16586,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
@@ -16610,7 +16619,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
@@ -16643,7 +16652,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -16655,7 +16664,7 @@
         <v>123</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>135</v>
@@ -16691,22 +16700,22 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16739,7 +16748,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -16759,7 +16768,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -16774,7 +16783,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -16794,7 +16803,7 @@
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
       <c t="s" r="M483" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
@@ -16809,7 +16818,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
@@ -16842,7 +16851,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F485" s="7">
         <v>321</v>
@@ -16890,7 +16899,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F487" s="7">
         <v>320</v>
@@ -16925,7 +16934,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F488" s="7">
         <v>320</v>
@@ -16943,11 +16952,11 @@
         <v>433</v>
       </c>
       <c t="s" r="K488" s="7">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -16962,7 +16971,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F489" s="7">
         <v>320</v>
@@ -16984,7 +16993,7 @@
       </c>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -16999,7 +17008,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F490" s="7">
         <v>320</v>
@@ -17036,7 +17045,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F491" s="7">
         <v>320</v>
@@ -17069,7 +17078,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F492" s="7">
         <v>320</v>
@@ -17102,7 +17111,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F493" s="7">
         <v>320</v>
@@ -17117,7 +17126,7 @@
         <v>343</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -17150,7 +17159,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
@@ -17159,13 +17168,13 @@
         <v>178</v>
       </c>
       <c t="s" r="H495" s="8">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c t="s" r="I495" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -17183,13 +17192,13 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F496" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G496" s="8">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c t="s" r="H496" s="8">
         <v>178</v>
@@ -17198,7 +17207,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -17231,13 +17240,13 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F498" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G498" s="8">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c t="s" r="H498" s="8">
         <v>141</v>
@@ -17246,7 +17255,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J498" s="7">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
@@ -17279,13 +17288,13 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F500" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G500" s="8">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c t="s" r="H500" s="8">
         <v>16</v>
@@ -17299,7 +17308,7 @@
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
       <c t="s" r="M500" s="7">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="501" ht="14.25" customHeight="1">
@@ -17314,7 +17323,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F501" s="7">
         <v>330</v>
@@ -17362,7 +17371,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F503" s="7">
         <v>330</v>
@@ -17371,7 +17380,7 @@
         <v>178</v>
       </c>
       <c t="s" r="H503" s="8">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="I503" s="7">
         <v>185</v>
@@ -17382,7 +17391,7 @@
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
       <c t="s" r="M503" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="504" ht="14.25" customHeight="1">
@@ -17397,13 +17406,13 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F504" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G504" s="8">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="H504" s="8">
         <v>178</v>
@@ -17445,7 +17454,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F506" s="7">
         <v>330</v>
@@ -17454,7 +17463,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H506" s="8">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c t="s" r="I506" s="7">
         <v>320</v>
@@ -17465,7 +17474,7 @@
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
       <c t="s" r="M506" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="507" ht="14.25" customHeight="1">
@@ -17480,13 +17489,13 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F507" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G507" s="8">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c t="s" r="H507" s="8">
         <v>16</v>
@@ -17528,7 +17537,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F509" s="7">
         <v>330</v>
@@ -17543,7 +17552,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J509" s="7">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
@@ -17563,7 +17572,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F510" s="7">
         <v>330</v>
@@ -17572,7 +17581,7 @@
         <v>141</v>
       </c>
       <c t="s" r="H510" s="8">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c t="s" r="I510" s="7">
         <v>288</v>
@@ -17583,7 +17592,7 @@
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
       <c t="s" r="M510" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="511" ht="14.25" customHeight="1">
@@ -17598,13 +17607,13 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F511" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G511" s="8">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c t="s" r="H511" s="8">
         <v>141</v>
@@ -17646,7 +17655,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F513" s="7">
         <v>330</v>
@@ -17655,7 +17664,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H513" s="8">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c t="s" r="I513" s="7">
         <v>207</v>
@@ -17666,7 +17675,7 @@
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
       <c t="s" r="M513" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="514" ht="14.25" customHeight="1">
@@ -17681,19 +17690,19 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F514" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G514" s="8">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c t="s" r="H514" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I514" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c t="s" r="J514" s="7">
         <v>329</v>
@@ -17704,7 +17713,7 @@
     </row>
     <row r="515" ht="16.5" customHeight="1">
       <c t="s" r="A515" s="9">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
@@ -17724,7 +17733,7 @@
     <row r="516" ht="65.25" customHeight="1"/>
     <row r="517" ht="16.5" customHeight="1">
       <c t="s" r="A517" s="10">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B517" s="10"/>
       <c r="C517" s="10"/>
@@ -17737,7 +17746,7 @@
       <c r="J517" s="10"/>
       <c r="K517" s="10"/>
       <c t="s" r="L517" s="11">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M517" s="11"/>
       <c r="N517" s="11"/>
